--- a/SCH-STH/Impact assessments/Mali/2025/ml_sch_sth_impact_2501_4_hemastix.xlsx
+++ b/SCH-STH/Impact assessments/Mali/2025/ml_sch_sth_impact_2501_4_hemastix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\SCH-STH\Impact assessments\Mali\2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F1F7F35-715E-4921-BDCA-61B528E17EDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{486E4935-CF6B-439F-A59B-D5ACF7E67A30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="94">
   <si>
     <t>type</t>
   </si>
@@ -135,9 +135,6 @@
     <t>select_one grading</t>
   </si>
   <si>
-    <t>Sélectionner le sous-district</t>
-  </si>
-  <si>
     <t>Code de l'Opérateur</t>
   </si>
   <si>
@@ -183,21 +180,9 @@
     <t>subdistrict_list= ${u_subdistrict}</t>
   </si>
   <si>
-    <t>u_sequential_code</t>
-  </si>
-  <si>
-    <t>u_sequential_code2</t>
-  </si>
-  <si>
     <t>u_code_id</t>
   </si>
   <si>
-    <t>Veuillez entrer le code séquentiel</t>
-  </si>
-  <si>
-    <t>Répétez le code séquentiel</t>
-  </si>
-  <si>
     <t>Veuillez enregistrer ce code unique de l’enfant dans les registres et les échantillons de labo </t>
   </si>
   <si>
@@ -225,12 +210,6 @@
     <t>Nombre d'œufs par 10 ml</t>
   </si>
   <si>
-    <t>ml_sch_sth_impact_2501_4_hemastix</t>
-  </si>
-  <si>
-    <t>(2025 Jan) - 4. SCH/STH - Urines</t>
-  </si>
-  <si>
     <t>string</t>
   </si>
   <si>
@@ -294,12 +273,6 @@
     <t>ml_ia_u_2501</t>
   </si>
   <si>
-    <t>concat(${u_recorder}, '_', ${u_site_id}, '_', ${u_sequential_code})</t>
-  </si>
-  <si>
-    <t>Cet identifiant a déjà été utilisé dans ce village.</t>
-  </si>
-  <si>
     <t>end repeat</t>
   </si>
   <si>
@@ -309,7 +282,28 @@
     <t>if (${C2} = 1,'',substring-after(${C1},${u_code_id}))</t>
   </si>
   <si>
-    <t>not(selected(${C3}, ${u_code_id}))</t>
+    <t>ml_sch_sth_impact_2501_4_hemastix_v2</t>
+  </si>
+  <si>
+    <t>(2025 Jan) - 4. SCH/STH - Urines V2</t>
+  </si>
+  <si>
+    <t>Sélectionner l'aire de santé</t>
+  </si>
+  <si>
+    <t>u_code_id2</t>
+  </si>
+  <si>
+    <t>not(selected(${C3}, ${u_code_id})) and regex(., '^\d{2}_\d{3}_\d{1,3}$')</t>
+  </si>
+  <si>
+    <t>Le code répéter doit être le même</t>
+  </si>
+  <si>
+    <t>. = ${u_code_id}</t>
+  </si>
+  <si>
+    <t>Soit, cet identifiant a déjà été utilisé dans ce village, soit le format du code est incorecte</t>
   </si>
 </sst>
 </file>
@@ -526,7 +520,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -653,9 +647,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -963,15 +954,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q34"/>
+  <dimension ref="A1:Q33"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="19.625" style="60" customWidth="1"/>
-    <col min="2" max="2" width="17.625" style="60" customWidth="1"/>
-    <col min="3" max="3" width="47.5" style="60" customWidth="1"/>
+    <col min="1" max="1" width="19.625" style="59" customWidth="1"/>
+    <col min="2" max="2" width="17.625" style="59" customWidth="1"/>
+    <col min="3" max="3" width="47.5" style="59" customWidth="1"/>
     <col min="4" max="4" width="47.375" style="21" customWidth="1"/>
     <col min="5" max="5" width="12.625" style="21" customWidth="1"/>
-    <col min="6" max="6" width="16.875" style="60" customWidth="1"/>
+    <col min="6" max="6" width="16.875" style="59" customWidth="1"/>
     <col min="7" max="7" width="29.5" style="21" customWidth="1"/>
     <col min="8" max="8" width="22" style="21" customWidth="1"/>
     <col min="9" max="9" width="22.625" style="21" customWidth="1"/>
@@ -1022,19 +1013,19 @@
         <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="N1" s="23" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="O1" s="23" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="P1" s="23" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="Q1" s="23" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:17" s="22" customFormat="1">
@@ -1045,7 +1036,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2" s="38"/>
       <c r="E2" s="36"/>
@@ -1065,7 +1056,7 @@
     </row>
     <row r="3" spans="1:17" s="44" customFormat="1">
       <c r="A3" s="37" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B3" s="40" t="s">
         <v>14</v>
@@ -1085,7 +1076,7 @@
       <c r="K3" s="42"/>
       <c r="L3" s="42"/>
       <c r="N3" s="24" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="O3" s="24"/>
       <c r="P3" s="24"/>
@@ -1093,13 +1084,13 @@
     </row>
     <row r="4" spans="1:17" s="44" customFormat="1">
       <c r="A4" s="37" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B4" s="40" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="41" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="D4" s="41"/>
       <c r="E4" s="42"/>
@@ -1115,20 +1106,20 @@
         <v>17</v>
       </c>
       <c r="N4" s="24" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="O4" s="24" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="P4" s="24"/>
       <c r="Q4" s="24"/>
     </row>
     <row r="5" spans="1:17" s="44" customFormat="1">
       <c r="A5" s="37" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B5" s="46" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C5" s="41" t="s">
         <v>18</v>
@@ -1144,26 +1135,26 @@
       </c>
       <c r="K5" s="42"/>
       <c r="L5" s="45" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N5" s="24" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="O5" s="24"/>
       <c r="P5" s="24" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="Q5" s="24"/>
     </row>
     <row r="6" spans="1:17" s="48" customFormat="1">
       <c r="A6" s="37" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B6" s="46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C6" s="38" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D6" s="38"/>
       <c r="E6" s="37"/>
@@ -1176,23 +1167,23 @@
       </c>
       <c r="K6" s="37"/>
       <c r="L6" s="47" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="N6" s="24" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="O6" s="21"/>
       <c r="P6" s="21"/>
       <c r="Q6" s="21" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="22" customFormat="1">
       <c r="A7" s="29" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C7" s="21"/>
       <c r="D7" s="21"/>
@@ -1201,7 +1192,7 @@
       <c r="G7" s="21"/>
       <c r="H7" s="30"/>
       <c r="I7" s="29" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="J7" s="29"/>
       <c r="K7" s="29"/>
@@ -1210,13 +1201,13 @@
     </row>
     <row r="8" spans="1:17" s="22" customFormat="1">
       <c r="A8" s="31" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B8" s="32" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D8" s="32"/>
       <c r="E8" s="31"/>
@@ -1232,10 +1223,10 @@
     </row>
     <row r="9" spans="1:17" s="22" customFormat="1">
       <c r="A9" s="29" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="C9" s="21"/>
       <c r="D9" s="21"/>
@@ -1244,7 +1235,7 @@
       <c r="G9" s="21"/>
       <c r="H9" s="30"/>
       <c r="I9" s="29" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="J9" s="29"/>
       <c r="K9" s="29"/>
@@ -1253,10 +1244,10 @@
     </row>
     <row r="10" spans="1:17" s="22" customFormat="1">
       <c r="A10" s="29" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C10" s="21"/>
       <c r="D10" s="21"/>
@@ -1265,53 +1256,61 @@
       <c r="G10" s="21"/>
       <c r="H10" s="30"/>
       <c r="I10" s="29" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="J10" s="29"/>
       <c r="K10" s="29"/>
       <c r="L10" s="29"/>
       <c r="M10" s="29"/>
     </row>
-    <row r="11" spans="1:17" s="52" customFormat="1">
+    <row r="11" spans="1:17" s="51" customFormat="1" ht="47.25">
       <c r="A11" s="37" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="49" t="s">
         <v>53</v>
-      </c>
-      <c r="C11" s="49" t="s">
-        <v>56</v>
       </c>
       <c r="D11" s="50"/>
       <c r="E11" s="42"/>
-      <c r="F11" s="51"/>
-      <c r="G11" s="50"/>
+      <c r="F11" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>93</v>
+      </c>
       <c r="H11" s="42"/>
       <c r="I11" s="42"/>
-      <c r="J11" s="37" t="s">
+      <c r="J11" s="42" t="s">
         <v>13</v>
       </c>
       <c r="K11" s="42"/>
       <c r="L11" s="42"/>
-      <c r="N11" s="22"/>
+      <c r="N11" s="27"/>
       <c r="O11" s="22"/>
       <c r="P11" s="22"/>
       <c r="Q11" s="22"/>
     </row>
-    <row r="12" spans="1:17" s="52" customFormat="1">
-      <c r="A12" s="42" t="s">
-        <v>20</v>
+    <row r="12" spans="1:17" s="51" customFormat="1" ht="31.5">
+      <c r="A12" s="37" t="s">
+        <v>19</v>
       </c>
       <c r="B12" s="37" t="s">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="C12" s="49" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="42"/>
-      <c r="F12" s="51"/>
-      <c r="G12" s="50"/>
+      <c r="F12" s="45" t="s">
+        <v>92</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>91</v>
+      </c>
       <c r="H12" s="42"/>
       <c r="I12" s="42"/>
       <c r="J12" s="42" t="s">
@@ -1324,214 +1323,182 @@
       <c r="P12" s="22"/>
       <c r="Q12" s="22"/>
     </row>
-    <row r="13" spans="1:17" s="52" customFormat="1" ht="47.25">
-      <c r="A13" s="37" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="C13" s="49" t="s">
-        <v>58</v>
-      </c>
-      <c r="D13" s="50"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="45" t="s">
-        <v>95</v>
-      </c>
-      <c r="G13" s="20" t="s">
-        <v>91</v>
-      </c>
-      <c r="H13" s="42"/>
-      <c r="I13" s="42" t="s">
-        <v>90</v>
-      </c>
+    <row r="13" spans="1:17" s="22" customFormat="1">
+      <c r="A13" s="45" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="45" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="52"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="45"/>
+      <c r="G13" s="52"/>
+      <c r="H13" s="45"/>
+      <c r="I13" s="45"/>
       <c r="J13" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="K13" s="42"/>
-      <c r="L13" s="42"/>
-      <c r="M13" s="52" t="s">
-        <v>13</v>
-      </c>
+      <c r="K13" s="45"/>
+      <c r="L13" s="45"/>
       <c r="N13" s="27"/>
-      <c r="O13" s="22"/>
-      <c r="P13" s="22"/>
-      <c r="Q13" s="22"/>
-    </row>
-    <row r="14" spans="1:17" s="22" customFormat="1">
-      <c r="A14" s="45" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" s="53" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" s="53"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="53"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="45"/>
+    </row>
+    <row r="14" spans="1:17" s="48" customFormat="1" ht="31.5">
+      <c r="A14" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="36" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" s="39"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="G14" s="39" t="s">
+        <v>59</v>
+      </c>
+      <c r="H14" s="36"/>
+      <c r="I14" s="36"/>
       <c r="J14" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="K14" s="45"/>
-      <c r="L14" s="45"/>
-      <c r="N14" s="27"/>
-    </row>
-    <row r="15" spans="1:17" s="48" customFormat="1" ht="31.5">
+      <c r="K14" s="36"/>
+      <c r="L14" s="36"/>
+      <c r="N14" s="28"/>
+      <c r="O14" s="21"/>
+      <c r="P14" s="21"/>
+      <c r="Q14" s="21"/>
+    </row>
+    <row r="15" spans="1:17" s="22" customFormat="1">
       <c r="A15" s="36" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="36" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="C15" s="39" t="s">
-        <v>62</v>
-      </c>
       <c r="D15" s="39"/>
-      <c r="E15" s="36"/>
-      <c r="F15" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="G15" s="39" t="s">
-        <v>64</v>
-      </c>
+      <c r="E15" s="53"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="54"/>
       <c r="H15" s="36"/>
-      <c r="I15" s="36"/>
-      <c r="J15" s="42" t="s">
+      <c r="I15" s="53"/>
+      <c r="J15" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="K15" s="36"/>
-      <c r="L15" s="36"/>
+      <c r="K15" s="53"/>
+      <c r="L15" s="53"/>
       <c r="N15" s="28"/>
-      <c r="O15" s="21"/>
-      <c r="P15" s="21"/>
-      <c r="Q15" s="21"/>
+      <c r="O15" s="24"/>
+      <c r="P15" s="24"/>
+      <c r="Q15" s="24"/>
     </row>
     <row r="16" spans="1:17" s="22" customFormat="1">
       <c r="A16" s="36" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B16" s="36" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="C16" s="39" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="D16" s="39"/>
-      <c r="E16" s="54"/>
+      <c r="E16" s="53"/>
       <c r="F16" s="36"/>
-      <c r="G16" s="55"/>
-      <c r="H16" s="36"/>
-      <c r="I16" s="54"/>
-      <c r="J16" s="36" t="s">
-        <v>13</v>
-      </c>
-      <c r="K16" s="54"/>
-      <c r="L16" s="54"/>
-      <c r="N16" s="28"/>
-      <c r="O16" s="24"/>
-      <c r="P16" s="24"/>
-      <c r="Q16" s="24"/>
-    </row>
-    <row r="17" spans="1:17" s="22" customFormat="1">
-      <c r="A17" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" s="36" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="39" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" s="39"/>
-      <c r="E17" s="54"/>
-      <c r="F17" s="36"/>
-      <c r="G17" s="55"/>
-      <c r="H17" s="54"/>
-      <c r="I17" s="54"/>
-      <c r="J17" s="36"/>
-      <c r="K17" s="54"/>
-      <c r="L17" s="54"/>
-      <c r="N17" s="27"/>
-    </row>
-    <row r="18" spans="1:17" customFormat="1">
-      <c r="A18" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="B18" s="26"/>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="26"/>
-      <c r="J18" s="26"/>
-      <c r="K18" s="26"/>
-      <c r="L18" s="26"/>
-      <c r="M18" s="26"/>
-      <c r="N18" s="26"/>
+      <c r="G16" s="54"/>
+      <c r="H16" s="53"/>
+      <c r="I16" s="53"/>
+      <c r="J16" s="36"/>
+      <c r="K16" s="53"/>
+      <c r="L16" s="53"/>
+      <c r="N16" s="27"/>
+    </row>
+    <row r="17" spans="1:17" customFormat="1">
+      <c r="A17" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B17" s="26"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="26"/>
+      <c r="I17" s="26"/>
+      <c r="J17" s="26"/>
+      <c r="K17" s="26"/>
+      <c r="L17" s="26"/>
+      <c r="M17" s="26"/>
+      <c r="N17" s="26"/>
+    </row>
+    <row r="18" spans="1:17" s="22" customFormat="1">
+      <c r="A18" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="56"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="53"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="54"/>
+      <c r="H18" s="53"/>
+      <c r="I18" s="53"/>
+      <c r="J18" s="36"/>
+      <c r="K18" s="53"/>
+      <c r="L18" s="53"/>
+      <c r="N18" s="27"/>
     </row>
     <row r="19" spans="1:17" s="22" customFormat="1">
       <c r="A19" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="56" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="57"/>
-      <c r="D19" s="58"/>
-      <c r="E19" s="54"/>
+        <v>25</v>
+      </c>
+      <c r="B19" s="55" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="56"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="53"/>
       <c r="F19" s="36"/>
-      <c r="G19" s="55"/>
-      <c r="H19" s="54"/>
-      <c r="I19" s="54"/>
+      <c r="G19" s="54"/>
+      <c r="H19" s="53"/>
+      <c r="I19" s="53"/>
       <c r="J19" s="36"/>
-      <c r="K19" s="54"/>
-      <c r="L19" s="54"/>
+      <c r="K19" s="53"/>
+      <c r="L19" s="53"/>
       <c r="N19" s="27"/>
     </row>
-    <row r="20" spans="1:17" s="22" customFormat="1">
-      <c r="A20" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="56" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" s="57"/>
-      <c r="D20" s="58"/>
-      <c r="E20" s="54"/>
-      <c r="F20" s="36"/>
-      <c r="G20" s="55"/>
-      <c r="H20" s="54"/>
-      <c r="I20" s="54"/>
+    <row r="20" spans="1:17">
+      <c r="A20" s="55"/>
+      <c r="B20" s="55"/>
+      <c r="C20" s="56"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="58"/>
+      <c r="F20" s="55"/>
+      <c r="G20" s="57"/>
+      <c r="H20" s="53"/>
+      <c r="I20" s="58"/>
       <c r="J20" s="36"/>
-      <c r="K20" s="54"/>
-      <c r="L20" s="54"/>
+      <c r="K20" s="58"/>
+      <c r="L20" s="58"/>
       <c r="N20" s="27"/>
+      <c r="O20" s="22"/>
+      <c r="P20" s="22"/>
+      <c r="Q20" s="22"/>
     </row>
     <row r="21" spans="1:17">
-      <c r="A21" s="56"/>
-      <c r="B21" s="56"/>
-      <c r="C21" s="57"/>
-      <c r="D21" s="58"/>
-      <c r="E21" s="59"/>
-      <c r="F21" s="56"/>
-      <c r="G21" s="58"/>
-      <c r="H21" s="54"/>
-      <c r="I21" s="59"/>
-      <c r="J21" s="36"/>
-      <c r="K21" s="59"/>
-      <c r="L21" s="59"/>
-      <c r="N21" s="27"/>
-      <c r="O21" s="22"/>
-      <c r="P21" s="22"/>
-      <c r="Q21" s="22"/>
+      <c r="N21" s="28"/>
     </row>
     <row r="22" spans="1:17">
       <c r="N22" s="28"/>
@@ -1549,19 +1516,16 @@
       <c r="N26" s="28"/>
     </row>
     <row r="27" spans="1:17">
-      <c r="N27" s="28"/>
-    </row>
-    <row r="28" spans="1:17">
-      <c r="N28" s="61"/>
-      <c r="O28" s="21"/>
-      <c r="P28" s="21"/>
-      <c r="Q28" s="21"/>
-    </row>
-    <row r="34" spans="14:17">
-      <c r="N34" s="21"/>
-      <c r="O34" s="21"/>
-      <c r="P34" s="21"/>
-      <c r="Q34" s="21"/>
+      <c r="N27" s="60"/>
+      <c r="O27" s="21"/>
+      <c r="P27" s="21"/>
+      <c r="Q27" s="21"/>
+    </row>
+    <row r="33" spans="14:17">
+      <c r="N33" s="21"/>
+      <c r="O33" s="21"/>
+      <c r="P33" s="21"/>
+      <c r="Q33" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1619,68 +1583,68 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -4085,10 +4049,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="22" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="C2" s="21" t="s">
         <v>34</v>

--- a/SCH-STH/Impact assessments/Mali/2025/ml_sch_sth_impact_2501_4_hemastix.xlsx
+++ b/SCH-STH/Impact assessments/Mali/2025/ml_sch_sth_impact_2501_4_hemastix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\SCH-STH\Impact assessments\Mali\2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{486E4935-CF6B-439F-A59B-D5ACF7E67A30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B164310E-DD2F-40F7-A9C2-32CB9ED5794E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="95">
   <si>
     <t>type</t>
   </si>
@@ -303,7 +303,10 @@
     <t>. = ${u_code_id}</t>
   </si>
   <si>
-    <t>Soit, cet identifiant a déjà été utilisé dans ce village, soit le format du code est incorecte</t>
+    <t>exemple: 12_123_1</t>
+  </si>
+  <si>
+    <t>Soit, cet identifiant a déjà été utilisé dans ce village, soit le format du code est incorecte. Exemple d'un code 34_567_890</t>
   </si>
 </sst>
 </file>
@@ -1263,7 +1266,7 @@
       <c r="L10" s="29"/>
       <c r="M10" s="29"/>
     </row>
-    <row r="11" spans="1:17" s="51" customFormat="1" ht="47.25">
+    <row r="11" spans="1:17" s="51" customFormat="1" ht="63">
       <c r="A11" s="37" t="s">
         <v>19</v>
       </c>
@@ -1273,13 +1276,15 @@
       <c r="C11" s="49" t="s">
         <v>53</v>
       </c>
-      <c r="D11" s="50"/>
+      <c r="D11" s="50" t="s">
+        <v>93</v>
+      </c>
       <c r="E11" s="42"/>
       <c r="F11" s="45" t="s">
         <v>90</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H11" s="42"/>
       <c r="I11" s="42"/>

--- a/SCH-STH/Impact assessments/Mali/2025/ml_sch_sth_impact_2501_4_hemastix.xlsx
+++ b/SCH-STH/Impact assessments/Mali/2025/ml_sch_sth_impact_2501_4_hemastix.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\SCH-STH\Impact assessments\Mali\2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B164310E-DD2F-40F7-A9C2-32CB9ED5794E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DDD5D10-0D9F-451A-99B1-A490A83859FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="99">
   <si>
     <t>type</t>
   </si>
@@ -282,31 +282,43 @@
     <t>if (${C2} = 1,'',substring-after(${C1},${u_code_id}))</t>
   </si>
   <si>
-    <t>ml_sch_sth_impact_2501_4_hemastix_v2</t>
-  </si>
-  <si>
-    <t>(2025 Jan) - 4. SCH/STH - Urines V2</t>
-  </si>
-  <si>
     <t>Sélectionner l'aire de santé</t>
   </si>
   <si>
-    <t>u_code_id2</t>
-  </si>
-  <si>
-    <t>not(selected(${C3}, ${u_code_id})) and regex(., '^\d{2}_\d{3}_\d{1,3}$')</t>
-  </si>
-  <si>
-    <t>Le code répéter doit être le même</t>
-  </si>
-  <si>
-    <t>. = ${u_code_id}</t>
-  </si>
-  <si>
     <t>exemple: 12_123_1</t>
   </si>
   <si>
-    <t>Soit, cet identifiant a déjà été utilisé dans ce village, soit le format du code est incorecte. Exemple d'un code 34_567_890</t>
+    <t>ml_sch_sth_impact_2501_4_hemastix_v3</t>
+  </si>
+  <si>
+    <t>(2025 Jan) - 4. SCH/STH - Urines V3</t>
+  </si>
+  <si>
+    <t>Veuillez entrer le code séquentiel</t>
+  </si>
+  <si>
+    <t>Répétez le code séquentiel</t>
+  </si>
+  <si>
+    <t>Le code répété doit être le même</t>
+  </si>
+  <si>
+    <t>u_sequential_code</t>
+  </si>
+  <si>
+    <t>u_sequential_code2</t>
+  </si>
+  <si>
+    <t>. = ${u_sequential_code}</t>
+  </si>
+  <si>
+    <t>concat(${u_site_id} , '_',  ${u_sequential_code})</t>
+  </si>
+  <si>
+    <t xml:space="preserve">not(selected(${C3}, ${u_code_id})) </t>
+  </si>
+  <si>
+    <t>Soit, cet identifiant a déjà été utilisé dans ce village, soit le format du code est incorecte. Exemple d'un code 567_890</t>
   </si>
 </sst>
 </file>
@@ -523,7 +535,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -675,6 +687,21 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -957,7 +984,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q33"/>
+  <dimension ref="A1:S34"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="19.625" style="59" customWidth="1"/>
@@ -978,7 +1005,7 @@
     <col min="18" max="16384" width="11" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="22" customFormat="1" ht="18.75">
+    <row r="1" spans="1:19" s="22" customFormat="1" ht="18.75">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1031,7 +1058,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:17" s="22" customFormat="1">
+    <row r="2" spans="1:19" s="22" customFormat="1">
       <c r="A2" s="37" t="s">
         <v>20</v>
       </c>
@@ -1057,7 +1084,7 @@
       <c r="P2" s="24"/>
       <c r="Q2" s="24"/>
     </row>
-    <row r="3" spans="1:17" s="44" customFormat="1">
+    <row r="3" spans="1:19" s="44" customFormat="1">
       <c r="A3" s="37" t="s">
         <v>62</v>
       </c>
@@ -1085,7 +1112,7 @@
       <c r="P3" s="24"/>
       <c r="Q3" s="24"/>
     </row>
-    <row r="4" spans="1:17" s="44" customFormat="1">
+    <row r="4" spans="1:19" s="44" customFormat="1">
       <c r="A4" s="37" t="s">
         <v>62</v>
       </c>
@@ -1093,7 +1120,7 @@
         <v>16</v>
       </c>
       <c r="C4" s="41" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D4" s="41"/>
       <c r="E4" s="42"/>
@@ -1117,7 +1144,7 @@
       <c r="P4" s="24"/>
       <c r="Q4" s="24"/>
     </row>
-    <row r="5" spans="1:17" s="44" customFormat="1">
+    <row r="5" spans="1:19" s="44" customFormat="1">
       <c r="A5" s="37" t="s">
         <v>62</v>
       </c>
@@ -1149,7 +1176,7 @@
       </c>
       <c r="Q5" s="24"/>
     </row>
-    <row r="6" spans="1:17" s="48" customFormat="1">
+    <row r="6" spans="1:19" s="48" customFormat="1">
       <c r="A6" s="37" t="s">
         <v>62</v>
       </c>
@@ -1181,7 +1208,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="22" customFormat="1">
+    <row r="7" spans="1:19" s="22" customFormat="1">
       <c r="A7" s="29" t="s">
         <v>75</v>
       </c>
@@ -1202,7 +1229,7 @@
       <c r="L7" s="29"/>
       <c r="M7" s="29"/>
     </row>
-    <row r="8" spans="1:17" s="22" customFormat="1">
+    <row r="8" spans="1:19" s="22" customFormat="1">
       <c r="A8" s="31" t="s">
         <v>77</v>
       </c>
@@ -1224,7 +1251,7 @@
       <c r="M8" s="31"/>
       <c r="N8" s="25"/>
     </row>
-    <row r="9" spans="1:17" s="22" customFormat="1">
+    <row r="9" spans="1:19" s="22" customFormat="1">
       <c r="A9" s="29" t="s">
         <v>75</v>
       </c>
@@ -1245,7 +1272,7 @@
       <c r="L9" s="29"/>
       <c r="M9" s="29"/>
     </row>
-    <row r="10" spans="1:17" s="22" customFormat="1">
+    <row r="10" spans="1:19" s="22" customFormat="1">
       <c r="A10" s="29" t="s">
         <v>75</v>
       </c>
@@ -1266,211 +1293,229 @@
       <c r="L10" s="29"/>
       <c r="M10" s="29"/>
     </row>
-    <row r="11" spans="1:17" s="51" customFormat="1" ht="63">
-      <c r="A11" s="37" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="37" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="D11" s="50" t="s">
+    <row r="11" spans="1:19" s="64" customFormat="1">
+      <c r="A11" s="61" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="62" t="s">
         <v>93</v>
       </c>
-      <c r="E11" s="42"/>
-      <c r="F11" s="45" t="s">
+      <c r="C11" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="G11" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="H11" s="42"/>
-      <c r="I11" s="42"/>
-      <c r="J11" s="42" t="s">
+      <c r="D11" s="20"/>
+      <c r="E11" s="61"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="61"/>
+      <c r="I11" s="62"/>
+      <c r="J11" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="K11" s="42"/>
-      <c r="L11" s="42"/>
-      <c r="N11" s="27"/>
+      <c r="K11" s="61"/>
+      <c r="L11" s="61"/>
+      <c r="M11" s="63"/>
+      <c r="N11" s="22"/>
       <c r="O11" s="22"/>
       <c r="P11" s="22"/>
       <c r="Q11" s="22"/>
-    </row>
-    <row r="12" spans="1:17" s="51" customFormat="1" ht="31.5">
-      <c r="A12" s="37" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="C12" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="D12" s="50"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="45" t="s">
+      <c r="R11" s="22"/>
+      <c r="S11" s="22"/>
+    </row>
+    <row r="12" spans="1:19" s="64" customFormat="1">
+      <c r="A12" s="61" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="62" t="s">
+        <v>94</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="D12" s="20"/>
+      <c r="E12" s="61"/>
+      <c r="F12" s="65" t="s">
+        <v>95</v>
+      </c>
+      <c r="G12" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="G12" s="20" t="s">
-        <v>91</v>
-      </c>
-      <c r="H12" s="42"/>
-      <c r="I12" s="42"/>
-      <c r="J12" s="42" t="s">
+      <c r="H12" s="61"/>
+      <c r="I12" s="62"/>
+      <c r="J12" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="K12" s="42"/>
-      <c r="L12" s="42"/>
-      <c r="N12" s="27"/>
+      <c r="K12" s="61"/>
+      <c r="L12" s="61"/>
+      <c r="M12" s="63"/>
+      <c r="N12" s="22"/>
       <c r="O12" s="22"/>
       <c r="P12" s="22"/>
       <c r="Q12" s="22"/>
-    </row>
-    <row r="13" spans="1:17" s="22" customFormat="1">
-      <c r="A13" s="45" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="45" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" s="52" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13" s="52"/>
-      <c r="E13" s="45"/>
-      <c r="F13" s="45"/>
-      <c r="G13" s="52"/>
-      <c r="H13" s="45"/>
-      <c r="I13" s="45"/>
+      <c r="R12" s="22"/>
+      <c r="S12" s="22"/>
+    </row>
+    <row r="13" spans="1:19" s="51" customFormat="1" ht="63">
+      <c r="A13" s="37" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="49" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="50" t="s">
+        <v>87</v>
+      </c>
+      <c r="E13" s="42"/>
+      <c r="F13" s="45" t="s">
+        <v>97</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42" t="s">
+        <v>96</v>
+      </c>
       <c r="J13" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="K13" s="45"/>
-      <c r="L13" s="45"/>
+      <c r="K13" s="42"/>
+      <c r="L13" s="42"/>
+      <c r="M13" s="51" t="s">
+        <v>13</v>
+      </c>
       <c r="N13" s="27"/>
-    </row>
-    <row r="14" spans="1:17" s="48" customFormat="1" ht="31.5">
-      <c r="A14" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="C14" s="39" t="s">
-        <v>57</v>
-      </c>
-      <c r="D14" s="39"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36" t="s">
-        <v>58</v>
-      </c>
-      <c r="G14" s="39" t="s">
-        <v>59</v>
-      </c>
-      <c r="H14" s="36"/>
-      <c r="I14" s="36"/>
+      <c r="O13" s="22"/>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="22"/>
+    </row>
+    <row r="14" spans="1:19" s="22" customFormat="1">
+      <c r="A14" s="45" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="45" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="52"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="52"/>
+      <c r="H14" s="45"/>
+      <c r="I14" s="45"/>
       <c r="J14" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="K14" s="36"/>
-      <c r="L14" s="36"/>
-      <c r="N14" s="28"/>
-      <c r="O14" s="21"/>
-      <c r="P14" s="21"/>
-      <c r="Q14" s="21"/>
-    </row>
-    <row r="15" spans="1:17" s="22" customFormat="1">
+      <c r="K14" s="45"/>
+      <c r="L14" s="45"/>
+      <c r="N14" s="27"/>
+    </row>
+    <row r="15" spans="1:19" s="48" customFormat="1" ht="31.5">
       <c r="A15" s="36" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="36" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="39"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="G15" s="39" t="s">
+        <v>59</v>
+      </c>
+      <c r="H15" s="36"/>
+      <c r="I15" s="36"/>
+      <c r="J15" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="K15" s="36"/>
+      <c r="L15" s="36"/>
+      <c r="N15" s="28"/>
+      <c r="O15" s="21"/>
+      <c r="P15" s="21"/>
+      <c r="Q15" s="21"/>
+    </row>
+    <row r="16" spans="1:19" s="22" customFormat="1">
+      <c r="A16" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="C15" s="39" t="s">
+      <c r="C16" s="39" t="s">
         <v>61</v>
-      </c>
-      <c r="D15" s="39"/>
-      <c r="E15" s="53"/>
-      <c r="F15" s="36"/>
-      <c r="G15" s="54"/>
-      <c r="H15" s="36"/>
-      <c r="I15" s="53"/>
-      <c r="J15" s="36" t="s">
-        <v>13</v>
-      </c>
-      <c r="K15" s="53"/>
-      <c r="L15" s="53"/>
-      <c r="N15" s="28"/>
-      <c r="O15" s="24"/>
-      <c r="P15" s="24"/>
-      <c r="Q15" s="24"/>
-    </row>
-    <row r="16" spans="1:17" s="22" customFormat="1">
-      <c r="A16" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="36" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="39" t="s">
-        <v>22</v>
       </c>
       <c r="D16" s="39"/>
       <c r="E16" s="53"/>
       <c r="F16" s="36"/>
       <c r="G16" s="54"/>
-      <c r="H16" s="53"/>
+      <c r="H16" s="36"/>
       <c r="I16" s="53"/>
-      <c r="J16" s="36"/>
+      <c r="J16" s="36" t="s">
+        <v>13</v>
+      </c>
       <c r="K16" s="53"/>
       <c r="L16" s="53"/>
-      <c r="N16" s="27"/>
-    </row>
-    <row r="17" spans="1:17" customFormat="1">
-      <c r="A17" s="26" t="s">
+      <c r="N16" s="28"/>
+      <c r="O16" s="24"/>
+      <c r="P16" s="24"/>
+      <c r="Q16" s="24"/>
+    </row>
+    <row r="17" spans="1:17" s="22" customFormat="1">
+      <c r="A17" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="39"/>
+      <c r="E17" s="53"/>
+      <c r="F17" s="36"/>
+      <c r="G17" s="54"/>
+      <c r="H17" s="53"/>
+      <c r="I17" s="53"/>
+      <c r="J17" s="36"/>
+      <c r="K17" s="53"/>
+      <c r="L17" s="53"/>
+      <c r="N17" s="27"/>
+    </row>
+    <row r="18" spans="1:17" customFormat="1">
+      <c r="A18" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="B17" s="26"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="26"/>
-      <c r="H17" s="26"/>
-      <c r="I17" s="26"/>
-      <c r="J17" s="26"/>
-      <c r="K17" s="26"/>
-      <c r="L17" s="26"/>
-      <c r="M17" s="26"/>
-      <c r="N17" s="26"/>
-    </row>
-    <row r="18" spans="1:17" s="22" customFormat="1">
-      <c r="A18" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="55" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="56"/>
-      <c r="D18" s="57"/>
-      <c r="E18" s="53"/>
-      <c r="F18" s="36"/>
-      <c r="G18" s="54"/>
-      <c r="H18" s="53"/>
-      <c r="I18" s="53"/>
-      <c r="J18" s="36"/>
-      <c r="K18" s="53"/>
-      <c r="L18" s="53"/>
-      <c r="N18" s="27"/>
+      <c r="B18" s="26"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="26"/>
+      <c r="I18" s="26"/>
+      <c r="J18" s="26"/>
+      <c r="K18" s="26"/>
+      <c r="L18" s="26"/>
+      <c r="M18" s="26"/>
+      <c r="N18" s="26"/>
     </row>
     <row r="19" spans="1:17" s="22" customFormat="1">
       <c r="A19" s="36" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B19" s="55" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C19" s="56"/>
       <c r="D19" s="57"/>
@@ -1484,26 +1529,42 @@
       <c r="L19" s="53"/>
       <c r="N19" s="27"/>
     </row>
-    <row r="20" spans="1:17">
-      <c r="A20" s="55"/>
-      <c r="B20" s="55"/>
+    <row r="20" spans="1:17" s="22" customFormat="1">
+      <c r="A20" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="55" t="s">
+        <v>26</v>
+      </c>
       <c r="C20" s="56"/>
       <c r="D20" s="57"/>
-      <c r="E20" s="58"/>
-      <c r="F20" s="55"/>
-      <c r="G20" s="57"/>
+      <c r="E20" s="53"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="54"/>
       <c r="H20" s="53"/>
-      <c r="I20" s="58"/>
+      <c r="I20" s="53"/>
       <c r="J20" s="36"/>
-      <c r="K20" s="58"/>
-      <c r="L20" s="58"/>
+      <c r="K20" s="53"/>
+      <c r="L20" s="53"/>
       <c r="N20" s="27"/>
-      <c r="O20" s="22"/>
-      <c r="P20" s="22"/>
-      <c r="Q20" s="22"/>
     </row>
     <row r="21" spans="1:17">
-      <c r="N21" s="28"/>
+      <c r="A21" s="55"/>
+      <c r="B21" s="55"/>
+      <c r="C21" s="56"/>
+      <c r="D21" s="57"/>
+      <c r="E21" s="58"/>
+      <c r="F21" s="55"/>
+      <c r="G21" s="57"/>
+      <c r="H21" s="53"/>
+      <c r="I21" s="58"/>
+      <c r="J21" s="36"/>
+      <c r="K21" s="58"/>
+      <c r="L21" s="58"/>
+      <c r="N21" s="27"/>
+      <c r="O21" s="22"/>
+      <c r="P21" s="22"/>
+      <c r="Q21" s="22"/>
     </row>
     <row r="22" spans="1:17">
       <c r="N22" s="28"/>
@@ -1521,16 +1582,19 @@
       <c r="N26" s="28"/>
     </row>
     <row r="27" spans="1:17">
-      <c r="N27" s="60"/>
-      <c r="O27" s="21"/>
-      <c r="P27" s="21"/>
-      <c r="Q27" s="21"/>
-    </row>
-    <row r="33" spans="14:17">
-      <c r="N33" s="21"/>
-      <c r="O33" s="21"/>
-      <c r="P33" s="21"/>
-      <c r="Q33" s="21"/>
+      <c r="N27" s="28"/>
+    </row>
+    <row r="28" spans="1:17">
+      <c r="N28" s="60"/>
+      <c r="O28" s="21"/>
+      <c r="P28" s="21"/>
+      <c r="Q28" s="21"/>
+    </row>
+    <row r="34" spans="14:17">
+      <c r="N34" s="21"/>
+      <c r="O34" s="21"/>
+      <c r="P34" s="21"/>
+      <c r="Q34" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4054,10 +4118,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="22" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C2" s="21" t="s">
         <v>34</v>
